--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28432,6 +28432,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1222" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>0.178000003099442</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>0.178000003099442</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="G1222" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28478,6 +28478,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1223">
+      <c r="A1223" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1223" t="n">
+        <v>81000</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>0.202000007033348</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>0.187999993562698</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="G1223" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28501,6 +28501,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1224">
+      <c r="A1224" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="G1224" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1225" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>0.195999994874001</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>0.195999994874001</v>
+      </c>
+      <c r="G1225" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28365,19 +28365,19 @@
     </row>
     <row r="1218">
       <c r="A1218" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1218" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="C1218" t="n">
         <v>0.189999997615814</v>
       </c>
       <c r="D1218" t="n">
-        <v>0.189999997615814</v>
+        <v>0.181999996304512</v>
       </c>
       <c r="E1218" t="n">
-        <v>0.189999997615814</v>
+        <v>0.181999996304512</v>
       </c>
       <c r="F1218" t="n">
         <v>0.189999997615814</v>
@@ -28388,7 +28388,7 @@
     </row>
     <row r="1219">
       <c r="A1219" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1219" t="n">
         <v>0</v>
@@ -28411,22 +28411,22 @@
     </row>
     <row r="1220">
       <c r="A1220" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1220" t="n">
-        <v>78000</v>
+        <v>0</v>
       </c>
       <c r="C1220" t="n">
-        <v>0.186000004410744</v>
+        <v>0.189999997615814</v>
       </c>
       <c r="D1220" t="n">
-        <v>0.178000003099442</v>
+        <v>0.189999997615814</v>
       </c>
       <c r="E1220" t="n">
-        <v>0.184000000357628</v>
+        <v>0.189999997615814</v>
       </c>
       <c r="F1220" t="n">
-        <v>0.186000004410744</v>
+        <v>0.189999997615814</v>
       </c>
       <c r="G1220" t="s">
         <v>7</v>
@@ -28434,19 +28434,19 @@
     </row>
     <row r="1221">
       <c r="A1221" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1221" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="C1221" t="n">
         <v>0.186000004410744</v>
       </c>
       <c r="D1221" t="n">
-        <v>0.186000004410744</v>
+        <v>0.178000003099442</v>
       </c>
       <c r="E1221" t="n">
-        <v>0.186000004410744</v>
+        <v>0.184000000357628</v>
       </c>
       <c r="F1221" t="n">
         <v>0.186000004410744</v>
@@ -28457,19 +28457,19 @@
     </row>
     <row r="1222">
       <c r="A1222" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1222" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="C1222" t="n">
         <v>0.186000004410744</v>
       </c>
       <c r="D1222" t="n">
-        <v>0.178000003099442</v>
+        <v>0.186000004410744</v>
       </c>
       <c r="E1222" t="n">
-        <v>0.178000003099442</v>
+        <v>0.186000004410744</v>
       </c>
       <c r="F1222" t="n">
         <v>0.186000004410744</v>
@@ -28480,22 +28480,22 @@
     </row>
     <row r="1223">
       <c r="A1223" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1223" t="n">
-        <v>81000</v>
+        <v>17000</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.202000007033348</v>
+        <v>0.186000004410744</v>
       </c>
       <c r="D1223" t="n">
+        <v>0.178000003099442</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>0.178000003099442</v>
+      </c>
+      <c r="F1223" t="n">
         <v>0.186000004410744</v>
-      </c>
-      <c r="E1223" t="n">
-        <v>0.187999993562698</v>
-      </c>
-      <c r="F1223" t="n">
-        <v>0.200000002980232</v>
       </c>
       <c r="G1223" t="s">
         <v>7</v>
@@ -28503,19 +28503,19 @@
     </row>
     <row r="1224">
       <c r="A1224" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1224" t="n">
-        <v>0</v>
+        <v>81000</v>
       </c>
       <c r="C1224" t="n">
-        <v>0.200000002980232</v>
+        <v>0.202000007033348</v>
       </c>
       <c r="D1224" t="n">
-        <v>0.200000002980232</v>
+        <v>0.186000004410744</v>
       </c>
       <c r="E1224" t="n">
-        <v>0.200000002980232</v>
+        <v>0.187999993562698</v>
       </c>
       <c r="F1224" t="n">
         <v>0.200000002980232</v>
@@ -28526,24 +28526,47 @@
     </row>
     <row r="1225">
       <c r="A1225" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1225" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="C1225" t="n">
         <v>0.200000002980232</v>
       </c>
       <c r="D1225" t="n">
-        <v>0.195999994874001</v>
+        <v>0.200000002980232</v>
       </c>
       <c r="E1225" t="n">
         <v>0.200000002980232</v>
       </c>
       <c r="F1225" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="G1225" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1226" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C1226" t="n">
         <v>0.195999994874001</v>
       </c>
-      <c r="G1225" t="s">
+      <c r="D1226" t="n">
+        <v>0.195999994874001</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>0.195999994874001</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>0.195999994874001</v>
+      </c>
+      <c r="G1226" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -32285,7 +32285,7 @@
         <v>34000</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.189999997615814</v>
+        <v>0.200000002980232</v>
       </c>
       <c r="D1228" t="n">
         <v>0.186000004410744</v>
@@ -32300,6 +32300,32 @@
         <v>0.200000002980232</v>
       </c>
       <c r="H1228" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1229" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="H1229" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -32329,6 +32329,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1230">
+      <c r="A1230" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1230" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="H1230" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -32459,6 +32459,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1235">
+      <c r="A1235" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1235" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="H1235" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28793,7 +28793,9 @@
       <c r="E1236" t="n">
         <v>0.19200000166893</v>
       </c>
-      <c r="F1236"/>
+      <c r="F1236" t="n">
+        <v>0.177000001072884</v>
+      </c>
       <c r="G1236" t="s">
         <v>7</v>
       </c>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28800,6 +28800,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1237">
+      <c r="A1237" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1237" t="n">
+        <v>0.177000001072884</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>0.177000001072884</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>0.177000001072884</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>0.177000001072884</v>
+      </c>
+      <c r="G1237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1238" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>0.175999999046326</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="F1238"/>
+      <c r="G1238" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28839,8 +28839,31 @@
       <c r="E1238" t="n">
         <v>0.184000000357628</v>
       </c>
-      <c r="F1238"/>
+      <c r="F1238" t="n">
+        <v>0.178000003099442</v>
+      </c>
       <c r="G1238" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1239" t="n">
+        <v>99000</v>
+      </c>
+      <c r="C1239" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>0.172999992966652</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="F1239"/>
+      <c r="G1239" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28862,8 +28862,31 @@
       <c r="E1239" t="n">
         <v>0.180000007152557</v>
       </c>
-      <c r="F1239"/>
+      <c r="F1239" t="n">
+        <v>0.175999999046326</v>
+      </c>
       <c r="G1239" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1240" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C1240" t="n">
+        <v>0.187000006437302</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>0.175999999046326</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>0.181999996304512</v>
+      </c>
+      <c r="F1240"/>
+      <c r="G1240" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28885,8 +28885,31 @@
       <c r="E1240" t="n">
         <v>0.181999996304512</v>
       </c>
-      <c r="F1240"/>
+      <c r="F1240" t="n">
+        <v>0.177000001072884</v>
+      </c>
       <c r="G1240" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1241" t="n">
+        <v>95000</v>
+      </c>
+      <c r="C1241" t="n">
+        <v>0.197999998927116</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>0.175999999046326</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="F1241"/>
+      <c r="G1241" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28908,7 +28908,9 @@
       <c r="E1241" t="n">
         <v>0.184000000357628</v>
       </c>
-      <c r="F1241"/>
+      <c r="F1241" t="n">
+        <v>0.195999994874001</v>
+      </c>
       <c r="G1241" t="s">
         <v>7</v>
       </c>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -28938,6 +28938,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1243">
+      <c r="A1243" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1243" t="n">
+        <v>89000</v>
+      </c>
+      <c r="C1243" t="n">
+        <v>0.203999996185303</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>0.18299999833107</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>0.203999996185303</v>
+      </c>
+      <c r="G1243" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -32745,6 +32745,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1246" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="H1246" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -32771,6 +32771,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1247">
+      <c r="A1247" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1247" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="H1247" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -36570,6 +36570,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1249">
+      <c r="A1249" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1249" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>0.186000004410744</v>
+      </c>
+      <c r="H1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1249" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1250" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="H1250" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -36628,6 +36628,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1251">
+      <c r="A1251" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1251" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="H1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1251" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -36657,6 +36657,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1252">
+      <c r="A1252" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1252" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="H1252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1253" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>0.184000000357628</v>
+      </c>
+      <c r="H1253" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -36715,6 +36715,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1254">
+      <c r="A1254" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1254" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1254" t="n">
+        <v>0.187999993562698</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>0.187999993562698</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="H1254" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1254" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -36744,6 +36744,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1255">
+      <c r="A1255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1255" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1255" t="n">
+        <v>0.194000005722046</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>0.203999996185303</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>0.189999997615814</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>0.197999998927116</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>0.197999998927116</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>57000</v>
+      </c>
+      <c r="I1255" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ALFO.MI.xlsx
+++ b/data/ALFO.MI.xlsx
@@ -36773,6 +36773,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1256">
+      <c r="A1256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1256" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>0.197999998927116</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>0.203999996185303</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>0.197999998927116</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>0.203999996185303</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>0.203999996185303</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I1256" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
